--- a/artfynd/S 1413-2026 artfynd.xlsx
+++ b/artfynd/S 1413-2026 artfynd.xlsx
@@ -3346,7 +3346,7 @@
         <v>97884791</v>
       </c>
       <c r="B28" t="n">
-        <v>89235</v>
+        <v>89237</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/S 1413-2026 artfynd.xlsx
+++ b/artfynd/S 1413-2026 artfynd.xlsx
@@ -3346,7 +3346,7 @@
         <v>97884791</v>
       </c>
       <c r="B28" t="n">
-        <v>89237</v>
+        <v>89239</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/S 1413-2026 artfynd.xlsx
+++ b/artfynd/S 1413-2026 artfynd.xlsx
@@ -3346,7 +3346,7 @@
         <v>97884791</v>
       </c>
       <c r="B28" t="n">
-        <v>89239</v>
+        <v>89241</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
